--- a/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
+++ b/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
@@ -149,8 +149,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MGAData" displayName="MGAData" ref="A1:V2" headerRowCount="1">
-  <autoFilter ref="A1:V2"/>
-  <tableColumns count="21">
+  <tableColumns count="22">
     <tableColumn id="1" name="Tenure Holder"/>
     <tableColumn id="2" name="RN"/>
     <tableColumn id="3" name="Bore assessment status"/>
@@ -172,6 +171,7 @@
     <tableColumn id="19" name="Replaces submission"/>
     <tableColumn id="20" name="Source"/>
     <tableColumn id="21" name="App version"/>
+    <tableColumn id="22" name="ClientRef"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -524,7 +524,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sheet Tenure holders: the access codes the flow checks. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company. EmailDomain must never be blank: the flow refuses a company whose domain is blank.</t>
+          <t>Sheet Tenure holders: the access codes the flow checks. The AccessCode column ships with placeholders: type your own codes before uploading (anything you can remember for the demo); the codes in this file are public because the file is in a public repository. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company. EmailDomain must never be blank: the flow refuses a company whose domain is blank.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARW-QVIK-J9VB</t>
+          <t>CHANGE-ME-ARROW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORG-YUB2-5R2X</t>
+          <t>CHANGE-ME-ORIGIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN-FXLD-N0G3</t>
+          <t>CHANGE-ME-SANTOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QGC-86MB-7V8U</t>
+          <t>CHANGE-ME-QGC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
+++ b/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arrow Energy</t>
+          <t>Arrow Energy (PILOT TEST)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Origin Energy (APLNG)</t>
+          <t>Origin Energy (APLNG) (PILOT TEST)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santos (GLNG)</t>
+          <t>Santos (GLNG) (PILOT TEST)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QGC (Shell)</t>
+          <t>QGC (Shell) (PILOT TEST)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
+++ b/bore_search_tool/power_automate/pilot/MGA_master_register_pilot.xlsx
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TenureHolders" displayName="TenureHolders" ref="A1:F5" headerRowCount="1">
-  <autoFilter ref="A1:F5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TenureHolders" displayName="TenureHolders" ref="A1:F11" headerRowCount="1">
+  <autoFilter ref="A1:F11"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="HolderName"/>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,198 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>PILOT: domain set to the department so the pilot owner can sign in as this company. Restore the real domain for go-live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SENEX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Senex Energy (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-SENEX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AGL (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-AGL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADZ ENERGY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADZ Energy (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-ADZ-ENERGY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRIDGEPORT ENERGY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bridgeport Energy (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-BRIDGEPORT-ENERGY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DENISON GAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Denison Gas (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-DENISON-GAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OGT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OGT (PILOT TEST)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHANGE-ME-OGT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>@dlgwv.qld.gov.au</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
         </is>
       </c>
     </row>
